--- a/results/alternatives/P2_earth_new_BASE/results.xlsx
+++ b/results/alternatives/P2_earth_new_BASE/results.xlsx
@@ -1520,19 +1520,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1630,7 +1630,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1710,7 +1710,7 @@
         <v>206.6988</v>
       </c>
       <c r="P4" t="n">
-        <v>9.301446</v>
+        <v>9.301446000000002</v>
       </c>
       <c r="Q4" t="n">
         <v>0.04500000000000001</v>
@@ -1722,7 +1722,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>27.12358500000006</v>
+        <v>27.12358500000005</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1736,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.105427357601002e-15</v>
+        <v>4.973799150320701e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1816,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-4.263256414560601e-14</v>
+        <v>4.263256414560601e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1864,16 +1864,16 @@
         <v>48.08260850000001</v>
       </c>
       <c r="N6" t="n">
-        <v>344.1154000000001</v>
+        <v>344.1154</v>
       </c>
       <c r="O6" t="n">
-        <v>344.1154000000001</v>
+        <v>344.1154</v>
       </c>
       <c r="P6" t="n">
         <v>15.485193</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.045</v>
+        <v>0.04499999999999999</v>
       </c>
       <c r="R6" t="n">
         <v>39.45205479452055</v>
@@ -1882,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>43.76750500000002</v>
+        <v>43.76750500000001</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>9.947598300641403e-14</v>
+        <v>4.263256414560601e-14</v>
       </c>
     </row>
     <row r="7">
@@ -1923,7 +1923,7 @@
         <v>390</v>
       </c>
       <c r="G7" t="n">
-        <v>250.0000000000001</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1944,16 +1944,16 @@
         <v>48.08264349999992</v>
       </c>
       <c r="N7" t="n">
-        <v>408.3769999999999</v>
+        <v>408.377</v>
       </c>
       <c r="O7" t="n">
-        <v>408.3769999999999</v>
+        <v>408.377</v>
       </c>
       <c r="P7" t="n">
         <v>18.376965</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04500000000000001</v>
+        <v>0.045</v>
       </c>
       <c r="R7" t="n">
         <v>48.08219178082192</v>
@@ -1962,7 +1962,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>48.08262599999995</v>
+        <v>48.08262599999997</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1976,7 +1976,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.4210854715202e-14</v>
+        <v>4.263256414560601e-14</v>
       </c>
     </row>
   </sheetData>
@@ -8356,10 +8356,10 @@
         <v>16.6988</v>
       </c>
       <c r="M15" t="n">
-        <v>16.69879999999999</v>
+        <v>16.6988</v>
       </c>
       <c r="N15" t="n">
-        <v>16.69879999999999</v>
+        <v>16.6988</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -8731,10 +8731,10 @@
         <v>80.8169</v>
       </c>
       <c r="M20" t="n">
-        <v>80.81689999999999</v>
+        <v>80.8169</v>
       </c>
       <c r="N20" t="n">
-        <v>80.81689999999999</v>
+        <v>80.8169</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -11221,7 +11221,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -22647,7 +22647,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>950.0000000000001</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -22667,7 +22667,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -22747,7 +22747,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -22787,7 +22787,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>67.18211550000001</v>
+        <v>67.18211549999999</v>
       </c>
     </row>
     <row r="15">
@@ -22847,7 +22847,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9996.593410000001</v>
+        <v>9996.593409999999</v>
       </c>
     </row>
     <row r="18">

--- a/results/alternatives/P2_earth_new_BASE/results.xlsx
+++ b/results/alternatives/P2_earth_new_BASE/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>0 / 0 / 19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -735,7 +879,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -750,7 +894,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -768,7 +912,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -783,7 +927,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -800,7 +944,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -815,7 +959,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -832,7 +976,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -847,7 +991,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -864,7 +1008,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -879,7 +1023,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -896,7 +1040,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -911,7 +1055,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -928,7 +1072,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -943,7 +1087,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -960,7 +1104,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -975,7 +1119,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -992,7 +1136,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1007,7 +1151,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1168,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1039,7 +1183,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1200,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1071,7 +1215,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1232,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1103,7 +1247,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1264,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1135,7 +1279,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1296,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1167,7 +1311,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1328,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1199,7 +1343,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1360,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1231,7 +1375,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1392,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1263,7 +1407,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1424,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1295,7 +1439,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1456,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1327,7 +1471,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1488,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1359,7 +1503,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10224,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>stock after inflow 70.434 t exceeds Base storage capacity 70.0 t within 2039-06 (before withdrawals)</t>
+          <t>запас после поступления 70.434 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-06 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10122,7 +10266,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stock after inflow 71.153 t exceeds Base storage capacity 70.0 t within 2039-07 (before withdrawals)</t>
+          <t>запас после поступления 71.153 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-07 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10164,7 +10308,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>stock after inflow 71.873 t exceeds Base storage capacity 70.0 t within 2039-08 (before withdrawals)</t>
+          <t>запас после поступления 71.873 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-08 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10206,7 +10350,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stock after inflow 72.592 t exceeds Base storage capacity 70.0 t within 2039-09 (before withdrawals)</t>
+          <t>запас после поступления 72.592 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-09 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10248,7 +10392,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>stock after inflow 73.311 t exceeds Base storage capacity 70.0 t within 2039-10 (before withdrawals)</t>
+          <t>запас после поступления 73.311 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-10 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -10290,7 +10434,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stock after inflow 74.030 t exceeds Base storage capacity 70.0 t within 2039-11 (before withdrawals)</t>
+          <t>запас после поступления 74.030 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-11 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -10332,7 +10476,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stock after inflow 74.749 t exceeds Base storage capacity 70.0 t within 2039-12 (before withdrawals)</t>
+          <t>запас после поступления 74.749 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-12 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -10374,7 +10518,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-01 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-01 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -10416,7 +10560,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-02 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-02 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -10458,7 +10602,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-03 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-03 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -10500,7 +10644,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-04 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-04 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -10542,7 +10686,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-05 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-05 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -10584,7 +10728,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-06 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-06 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -10626,7 +10770,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-07 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-07 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -10668,7 +10812,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-08 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-08 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -10710,7 +10854,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-09 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-09 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -10752,7 +10896,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-10 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-10 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -10794,7 +10938,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-11 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-11 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -10836,7 +10980,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stock after inflow 80.583 t exceeds Base storage capacity 70.0 t within 2040-12 (before withdrawals)</t>
+          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-12 (до выдачи потребителям)</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -12233,7 +12377,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -12246,7 +12390,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12282,7 +12426,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -12295,7 +12439,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12475,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12344,7 +12488,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12524,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12393,7 +12537,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12429,7 +12573,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12442,7 +12586,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12622,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12491,7 +12635,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13379,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -13245,7 +13389,7 @@
         <v/>
       </c>
       <c r="I50" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -13568,7 +13712,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -13578,7 +13722,7 @@
         <v/>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -14504,7 +14648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14573,6 +14717,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14628,6 +14777,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14683,6 +14837,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14738,6 +14897,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14793,6 +14957,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14848,6 +15017,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14903,6 +15077,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14958,6 +15137,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15013,6 +15197,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15068,6 +15257,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15123,6 +15317,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15178,6 +15377,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -15233,6 +15437,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15288,6 +15497,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -15343,6 +15557,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15398,6 +15617,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15453,6 +15677,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -15508,6 +15737,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -15563,6 +15797,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -15618,6 +15857,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -15673,6 +15917,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -15728,6 +15977,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -15783,6 +16037,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15838,6 +16097,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15893,6 +16157,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15948,6 +16217,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15988,11 +16262,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2035-01</t>
+          <t>2037-01</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -16001,7 +16275,12 @@
         </is>
       </c>
       <c r="M27" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -16058,6 +16337,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -16098,11 +16382,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2035-02</t>
+          <t>2037-02</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -16111,7 +16395,12 @@
         </is>
       </c>
       <c r="M29" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -16168,6 +16457,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -16208,11 +16502,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2035-03</t>
+          <t>2037-03</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -16221,7 +16515,12 @@
         </is>
       </c>
       <c r="M31" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -16278,6 +16577,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -16318,11 +16622,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2035-04</t>
+          <t>2037-04</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -16331,7 +16635,12 @@
         </is>
       </c>
       <c r="M33" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -16388,6 +16697,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -16428,11 +16742,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2035-05</t>
+          <t>2037-05</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -16441,7 +16755,12 @@
         </is>
       </c>
       <c r="M35" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -16498,6 +16817,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -16538,11 +16862,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2035-06</t>
+          <t>2037-06</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -16551,7 +16875,12 @@
         </is>
       </c>
       <c r="M37" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -16608,6 +16937,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -16648,11 +16982,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2035-07</t>
+          <t>2037-07</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -16661,7 +16995,12 @@
         </is>
       </c>
       <c r="M39" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -16718,6 +17057,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -16758,11 +17102,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2035-08</t>
+          <t>2037-08</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -16771,7 +17115,12 @@
         </is>
       </c>
       <c r="M41" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -16828,6 +17177,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16868,11 +17222,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J43" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2035-09</t>
+          <t>2037-09</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -16881,7 +17235,12 @@
         </is>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -16938,6 +17297,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16978,11 +17342,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2035-10</t>
+          <t>2037-10</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -16991,7 +17355,12 @@
         </is>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -17048,6 +17417,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -17088,11 +17462,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2035-11</t>
+          <t>2037-11</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -17101,7 +17475,12 @@
         </is>
       </c>
       <c r="M47" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -17158,6 +17537,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -17198,11 +17582,11 @@
         <v>1.391566666666667</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2035-12</t>
+          <t>2037-12</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -17211,7 +17595,12 @@
         </is>
       </c>
       <c r="M49" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -17268,6 +17657,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -17308,11 +17702,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2036-01</t>
+          <t>2038-01</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -17321,7 +17715,12 @@
         </is>
       </c>
       <c r="M51" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -17378,6 +17777,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -17418,11 +17822,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2036-02</t>
+          <t>2038-02</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -17431,7 +17835,12 @@
         </is>
       </c>
       <c r="M53" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -17488,6 +17897,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -17528,11 +17942,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J55" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2036-03</t>
+          <t>2038-03</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -17541,7 +17955,12 @@
         </is>
       </c>
       <c r="M55" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -17598,6 +18017,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -17638,11 +18062,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J57" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2036-04</t>
+          <t>2038-04</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -17651,7 +18075,12 @@
         </is>
       </c>
       <c r="M57" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -17708,6 +18137,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -17748,11 +18182,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J59" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2036-05</t>
+          <t>2038-05</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -17761,7 +18195,12 @@
         </is>
       </c>
       <c r="M59" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -17818,6 +18257,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17858,11 +18302,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J61" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2036-06</t>
+          <t>2038-06</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -17871,7 +18315,12 @@
         </is>
       </c>
       <c r="M61" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -17928,6 +18377,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17968,11 +18422,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J63" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2036-07</t>
+          <t>2038-07</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -17981,7 +18435,12 @@
         </is>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -18038,6 +18497,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -18078,11 +18542,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J65" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2036-08</t>
+          <t>2038-08</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -18091,7 +18555,12 @@
         </is>
       </c>
       <c r="M65" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -18148,6 +18617,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -18188,11 +18662,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J67" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2036-09</t>
+          <t>2038-09</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -18201,7 +18675,12 @@
         </is>
       </c>
       <c r="M67" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -18258,6 +18737,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -18298,11 +18782,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J69" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2036-10</t>
+          <t>2038-10</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -18311,7 +18795,12 @@
         </is>
       </c>
       <c r="M69" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -18368,6 +18857,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18408,11 +18902,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J71" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2036-11</t>
+          <t>2038-11</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -18421,7 +18915,12 @@
         </is>
       </c>
       <c r="M71" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -18478,6 +18977,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18518,11 +19022,11 @@
         <v>6.734741666666667</v>
       </c>
       <c r="J73" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2036-12</t>
+          <t>2038-12</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -18531,7 +19035,12 @@
         </is>
       </c>
       <c r="M73" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -18588,6 +19097,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -18643,6 +19157,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -18683,20 +19202,25 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J76" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
+          <t>2039-01</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
           <t>2037-01</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2037-01</t>
-        </is>
-      </c>
       <c r="M76" t="b">
         <v>1</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -18753,6 +19277,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -18808,6 +19337,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18848,11 +19382,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J79" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2037-02</t>
+          <t>2039-02</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -18862,6 +19396,11 @@
       </c>
       <c r="M79" t="b">
         <v>1</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -18918,6 +19457,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18973,6 +19517,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -19013,11 +19562,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J82" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2037-03</t>
+          <t>2039-03</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -19027,6 +19576,11 @@
       </c>
       <c r="M82" t="b">
         <v>1</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -19083,6 +19637,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -19138,6 +19697,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -19178,11 +19742,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J85" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2037-04</t>
+          <t>2039-04</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -19192,6 +19756,11 @@
       </c>
       <c r="M85" t="b">
         <v>1</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -19248,6 +19817,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -19303,6 +19877,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -19343,11 +19922,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J88" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2037-05</t>
+          <t>2039-05</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -19357,6 +19936,11 @@
       </c>
       <c r="M88" t="b">
         <v>1</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -19413,6 +19997,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -19468,6 +20057,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -19508,11 +20102,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J91" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2037-06</t>
+          <t>2039-06</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -19522,6 +20116,11 @@
       </c>
       <c r="M91" t="b">
         <v>1</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -19578,6 +20177,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -19633,6 +20237,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -19673,11 +20282,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J94" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2037-07</t>
+          <t>2039-07</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -19687,6 +20296,11 @@
       </c>
       <c r="M94" t="b">
         <v>1</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -19743,6 +20357,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -19798,6 +20417,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19838,11 +20462,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J97" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2037-08</t>
+          <t>2039-08</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -19852,6 +20476,11 @@
       </c>
       <c r="M97" t="b">
         <v>1</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -19908,6 +20537,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19963,6 +20597,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -20003,11 +20642,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J100" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2037-09</t>
+          <t>2039-09</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -20017,6 +20656,11 @@
       </c>
       <c r="M100" t="b">
         <v>1</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -20073,6 +20717,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -20128,6 +20777,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -20168,11 +20822,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J103" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2037-10</t>
+          <t>2039-10</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -20182,6 +20836,11 @@
       </c>
       <c r="M103" t="b">
         <v>1</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -20238,6 +20897,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -20293,6 +20957,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -20333,11 +21002,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J106" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2037-11</t>
+          <t>2039-11</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -20347,6 +21016,11 @@
       </c>
       <c r="M106" t="b">
         <v>1</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -20403,6 +21077,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -20458,6 +21137,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -20498,11 +21182,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J109" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2037-12</t>
+          <t>2039-12</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -20512,6 +21196,11 @@
       </c>
       <c r="M109" t="b">
         <v>1</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -20568,6 +21257,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -20623,6 +21317,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -20663,11 +21362,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J112" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2038-01</t>
+          <t>2040-01</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -20677,6 +21376,11 @@
       </c>
       <c r="M112" t="b">
         <v>1</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -20733,6 +21437,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -20788,6 +21497,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20828,11 +21542,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J115" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2038-02</t>
+          <t>2040-02</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -20842,6 +21556,11 @@
       </c>
       <c r="M115" t="b">
         <v>1</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -20898,6 +21617,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20953,6 +21677,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20993,11 +21722,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J118" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2038-03</t>
+          <t>2040-03</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -21007,6 +21736,11 @@
       </c>
       <c r="M118" t="b">
         <v>1</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -21063,6 +21797,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -21118,6 +21857,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -21158,11 +21902,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J121" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2038-04</t>
+          <t>2040-04</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -21172,6 +21916,11 @@
       </c>
       <c r="M121" t="b">
         <v>1</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -21228,6 +21977,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -21283,6 +22037,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -21323,11 +22082,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J124" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2038-05</t>
+          <t>2040-05</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -21337,6 +22096,11 @@
       </c>
       <c r="M124" t="b">
         <v>1</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -21393,6 +22157,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21448,6 +22217,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -21488,11 +22262,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J127" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2038-06</t>
+          <t>2040-06</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -21502,6 +22276,11 @@
       </c>
       <c r="M127" t="b">
         <v>1</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -21558,6 +22337,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -21613,6 +22397,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -21653,11 +22442,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J130" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2038-07</t>
+          <t>2040-07</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -21667,6 +22456,11 @@
       </c>
       <c r="M130" t="b">
         <v>1</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -21723,6 +22517,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -21778,6 +22577,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21818,11 +22622,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J133" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2038-08</t>
+          <t>2040-08</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -21832,6 +22636,11 @@
       </c>
       <c r="M133" t="b">
         <v>1</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -21888,6 +22697,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21943,6 +22757,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21983,11 +22802,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J136" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2038-09</t>
+          <t>2040-09</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -21997,6 +22816,11 @@
       </c>
       <c r="M136" t="b">
         <v>1</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -22053,6 +22877,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -22108,6 +22937,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -22148,11 +22982,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J139" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2038-10</t>
+          <t>2040-10</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -22162,6 +22996,11 @@
       </c>
       <c r="M139" t="b">
         <v>1</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -22218,6 +23057,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -22273,6 +23117,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -22313,11 +23162,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J142" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2038-11</t>
+          <t>2040-11</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -22327,6 +23176,11 @@
       </c>
       <c r="M142" t="b">
         <v>1</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -22383,6 +23237,11 @@
       <c r="M143" t="b">
         <v>1</v>
       </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -22438,6 +23297,11 @@
       <c r="M144" t="b">
         <v>1</v>
       </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -22478,11 +23342,11 @@
         <v>10.83333333333333</v>
       </c>
       <c r="J145" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2038-12</t>
+          <t>2040-12</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -22492,6 +23356,11 @@
       </c>
       <c r="M145" t="b">
         <v>1</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>ввод 2037-01 = решение 2035-01 + 24 мес. подготовки; срок заказа после ввода 0 мес. (допущение earth_new_post_commissioning_lead_months)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -23087,7 +23956,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/results/alternatives/P2_earth_new_BASE/results.xlsx
+++ b/results/alternatives/P2_earth_new_BASE/results.xlsx
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1504,6 +1504,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -12366,18 +12399,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -12390,7 +12423,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12415,18 +12448,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -12439,7 +12472,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12464,18 +12497,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12488,7 +12521,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12513,18 +12546,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12537,7 +12570,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12562,18 +12595,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12586,7 +12619,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12611,18 +12644,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12635,7 +12668,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12660,7 +12693,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -12684,7 +12717,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12928,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -12919,7 +12952,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13130,7 +13163,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -13154,7 +13187,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13463,7 +13496,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -13487,7 +13520,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13829,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -13820,7 +13853,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14260,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -14251,7 +14284,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/alternatives/P2_earth_new_BASE/results.xlsx
+++ b/results/alternatives/P2_earth_new_BASE/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -831,7 +831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,6 +1536,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/alternatives/P2_earth_new_BASE/results.xlsx
+++ b/results/alternatives/P2_earth_new_BASE/results.xlsx
@@ -7499,7 +7499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7608,6 +7608,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7683,6 +7688,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7758,6 +7766,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7833,6 +7844,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7908,6 +7922,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -7983,6 +8000,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8058,6 +8078,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8133,6 +8156,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8208,6 +8234,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8283,6 +8312,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8358,6 +8390,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8433,6 +8468,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8508,6 +8546,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8583,6 +8624,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8658,6 +8702,9 @@
       <c r="U15" t="n">
         <v>5.0097</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8733,6 +8780,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8808,6 +8858,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8883,6 +8936,9 @@
       <c r="U18" t="n">
         <v>85.5</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8958,6 +9014,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9033,6 +9092,9 @@
       <c r="U20" t="n">
         <v>24.2451</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9108,6 +9170,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9183,6 +9248,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9258,6 +9326,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9333,6 +9404,9 @@
       <c r="U24" t="n">
         <v>3.6174</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9408,6 +9482,9 @@
       <c r="U25" t="n">
         <v>39</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9483,6 +9560,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9558,6 +9638,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9633,6 +9716,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9708,6 +9794,9 @@
       <c r="U29" t="n">
         <v>13.25655</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9783,6 +9872,9 @@
       <c r="U30" t="n">
         <v>39</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9858,6 +9950,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9931,6 +10026,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9945,7 +10043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10009,6 +10107,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10051,6 +10154,9 @@
       <c r="L2" t="n">
         <v>360</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10093,6 +10199,9 @@
       <c r="L3" t="n">
         <v>360</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10135,6 +10244,9 @@
       <c r="L4" t="n">
         <v>360</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10177,6 +10289,9 @@
       <c r="L5" t="n">
         <v>360</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10219,6 +10334,9 @@
       <c r="L6" t="n">
         <v>360</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10260,6 +10378,9 @@
       </c>
       <c r="L7" t="n">
         <v>360</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23506,7 +23627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23944,11 +24065,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23964,11 +24085,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48.08264349999992</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -23984,11 +24105,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>48.08264349999992</v>
       </c>
     </row>
     <row r="25">
@@ -24004,7 +24125,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -24024,11 +24145,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -24044,11 +24165,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="28">
@@ -24064,11 +24185,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>75</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -24084,10 +24205,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>75</v>
       </c>
     </row>

--- a/results/alternatives/P2_earth_new_BASE/results.xlsx
+++ b/results/alternatives/P2_earth_new_BASE/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -470,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
     </row>
@@ -482,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0 / 0 / 19</t>
+          <t>19 / 0 / 0</t>
         </is>
       </c>
     </row>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -831,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1355,7 +1357,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1375,24 +1377,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1402,29 +1404,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1434,29 +1436,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1466,176 +1468,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2372,6 +2517,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2444,6 +2599,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2515,6 +2676,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2586,6 +2753,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2657,6 +2830,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2728,6 +2907,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2799,6 +2984,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2870,6 +3061,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2941,6 +3138,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3012,6 +3215,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3083,6 +3292,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3154,6 +3369,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3225,6 +3446,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3296,6 +3523,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3367,6 +3600,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3438,6 +3677,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3509,6 +3754,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3580,6 +3831,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3651,6 +3908,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3722,6 +3985,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3793,6 +4062,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3864,6 +4139,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3935,6 +4216,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4006,6 +4293,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4077,6 +4370,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4148,6 +4447,12 @@
         <v>1.423987865000004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.87468750000008</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4219,6 +4524,12 @@
         <v>1.460974635000005</v>
       </c>
       <c r="U27" t="n">
+        <v>40.49113366666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4290,6 +4601,12 @@
         <v>1.497961405000004</v>
       </c>
       <c r="U28" t="n">
+        <v>41.1075798333334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4361,6 +4678,12 @@
         <v>1.534948175000004</v>
       </c>
       <c r="U29" t="n">
+        <v>41.72402600000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4432,6 +4755,12 @@
         <v>1.571934945000004</v>
       </c>
       <c r="U30" t="n">
+        <v>42.34047216666673</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4503,6 +4832,12 @@
         <v>1.608921715000003</v>
       </c>
       <c r="U31" t="n">
+        <v>42.95691833333339</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4574,6 +4909,12 @@
         <v>1.645908485000003</v>
       </c>
       <c r="U32" t="n">
+        <v>43.57336450000005</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4645,6 +4986,12 @@
         <v>1.682895255000003</v>
       </c>
       <c r="U33" t="n">
+        <v>44.18981066666672</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4716,6 +5063,12 @@
         <v>1.719882025000002</v>
       </c>
       <c r="U34" t="n">
+        <v>44.80625683333338</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4787,6 +5140,12 @@
         <v>1.756868795000002</v>
       </c>
       <c r="U35" t="n">
+        <v>45.42270300000004</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4858,6 +5217,12 @@
         <v>1.793855565000002</v>
       </c>
       <c r="U36" t="n">
+        <v>46.0391491666667</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4929,6 +5294,12 @@
         <v>1.830842335000002</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65559533333337</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5000,6 +5371,12 @@
         <v>1.870911068750002</v>
       </c>
       <c r="U38" t="n">
+        <v>52.37477362500003</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5071,6 +5448,12 @@
         <v>1.914061766250002</v>
       </c>
       <c r="U39" t="n">
+        <v>53.0939519166667</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5142,6 +5525,12 @@
         <v>1.957212463750002</v>
       </c>
       <c r="U40" t="n">
+        <v>53.81313020833337</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5213,6 +5602,12 @@
         <v>2.000363161250002</v>
       </c>
       <c r="U41" t="n">
+        <v>54.53230850000003</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5284,6 +5679,12 @@
         <v>2.043513858750002</v>
       </c>
       <c r="U42" t="n">
+        <v>55.2514867916667</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5355,6 +5756,12 @@
         <v>2.086664556250002</v>
       </c>
       <c r="U43" t="n">
+        <v>55.97066508333337</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5426,6 +5833,12 @@
         <v>2.129815253750002</v>
       </c>
       <c r="U44" t="n">
+        <v>56.68984337500003</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5497,6 +5910,12 @@
         <v>2.172965951250001</v>
       </c>
       <c r="U45" t="n">
+        <v>57.4090216666667</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5568,6 +5987,12 @@
         <v>2.216116648750001</v>
       </c>
       <c r="U46" t="n">
+        <v>58.12819995833336</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5639,6 +6064,12 @@
         <v>2.259267346250001</v>
       </c>
       <c r="U47" t="n">
+        <v>58.84737825000003</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5710,6 +6141,12 @@
         <v>2.302418043750001</v>
       </c>
       <c r="U48" t="n">
+        <v>59.56655654166669</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5781,6 +6218,12 @@
         <v>2.345568741250001</v>
       </c>
       <c r="U49" t="n">
+        <v>60.28573483333336</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5852,6 +6295,12 @@
         <v>2.388719607500001</v>
       </c>
       <c r="U50" t="n">
+        <v>66.83825208333336</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5923,6 +6372,12 @@
         <v>2.431870642500001</v>
       </c>
       <c r="U51" t="n">
+        <v>67.55743600000002</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5994,6 +6449,12 @@
         <v>2.475021677500001</v>
       </c>
       <c r="U52" t="n">
+        <v>68.27661991666669</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6065,6 +6526,12 @@
         <v>2.518172712500001</v>
       </c>
       <c r="U53" t="n">
+        <v>68.99580383333335</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6136,6 +6603,12 @@
         <v>2.561323747500001</v>
       </c>
       <c r="U54" t="n">
+        <v>69.71498775000002</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6207,6 +6680,12 @@
         <v>2.604474782500001</v>
       </c>
       <c r="U55" t="n">
+        <v>70.43417166666669</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6278,6 +6757,12 @@
         <v>2.647625817500001</v>
       </c>
       <c r="U56" t="n">
+        <v>71.15335558333335</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6349,6 +6834,12 @@
         <v>2.690776852500001</v>
       </c>
       <c r="U57" t="n">
+        <v>71.87253950000002</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6420,6 +6911,12 @@
         <v>2.733927887500001</v>
       </c>
       <c r="U58" t="n">
+        <v>72.59172341666668</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6491,6 +6988,12 @@
         <v>2.777078922500001</v>
       </c>
       <c r="U59" t="n">
+        <v>73.31090733333335</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6562,6 +7065,12 @@
         <v>2.8202299575</v>
       </c>
       <c r="U60" t="n">
+        <v>74.03009125000001</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6633,6 +7142,12 @@
         <v>2.8633809925</v>
       </c>
       <c r="U61" t="n">
+        <v>74.74927516666668</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6704,6 +7219,12 @@
         <v>2.8849565975</v>
       </c>
       <c r="U62" t="n">
+        <v>80.58261141666668</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6775,6 +7296,12 @@
         <v>2.884956772499999</v>
       </c>
       <c r="U63" t="n">
+        <v>80.58261433333334</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6846,6 +7373,12 @@
         <v>2.884956947499999</v>
       </c>
       <c r="U64" t="n">
+        <v>80.58261725</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6917,6 +7450,12 @@
         <v>2.884957122499999</v>
       </c>
       <c r="U65" t="n">
+        <v>80.58262016666666</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6988,6 +7527,12 @@
         <v>2.884957297499998</v>
       </c>
       <c r="U66" t="n">
+        <v>80.58262308333332</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7059,6 +7604,12 @@
         <v>2.884957472499998</v>
       </c>
       <c r="U67" t="n">
+        <v>80.58262599999998</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7130,6 +7681,12 @@
         <v>2.884957647499997</v>
       </c>
       <c r="U68" t="n">
+        <v>80.58262891666664</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7201,6 +7758,12 @@
         <v>2.884957822499997</v>
       </c>
       <c r="U69" t="n">
+        <v>80.58263183333329</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7272,6 +7835,12 @@
         <v>2.884957997499997</v>
       </c>
       <c r="U70" t="n">
+        <v>80.58263474999995</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7343,6 +7912,12 @@
         <v>2.884958172499996</v>
       </c>
       <c r="U71" t="n">
+        <v>80.58263766666661</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7414,6 +7989,12 @@
         <v>2.884958347499996</v>
       </c>
       <c r="U72" t="n">
+        <v>80.58264058333327</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7485,6 +8066,12 @@
         <v>2.884958522499995</v>
       </c>
       <c r="U73" t="n">
+        <v>80.58264349999993</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10134,7 +10721,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10143,13 +10730,13 @@
         <v>360</v>
       </c>
       <c r="I2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1218.16123728</v>
+        <v>1218.53110305</v>
       </c>
       <c r="L2" t="n">
         <v>360</v>
@@ -10472,12 +11059,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>запас после поступления 70.434 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-06 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 70.434 т превышает ёмкость хранилища Base storage 70.0 т в 2039-06 (поставка одной партией в начале месяца; запас на начало 43.048 т, нетто-поступление 27.386 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -10514,12 +11101,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>запас после поступления 71.153 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-07 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 71.153 т превышает ёмкость хранилища Base storage 70.0 т в 2039-07 (поставка одной партией в начале месяца; запас на начало 43.768 т, нетто-поступление 27.386 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -10556,12 +11143,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>запас после поступления 71.873 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-08 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 71.873 т превышает ёмкость хранилища Base storage 70.0 т в 2039-08 (поставка одной партией в начале месяца; запас на начало 44.487 т, нетто-поступление 27.386 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -10598,12 +11185,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>запас после поступления 72.592 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-09 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 72.592 т превышает ёмкость хранилища Base storage 70.0 т в 2039-09 (поставка одной партией в начале месяца; запас на начало 45.206 т, нетто-поступление 27.386 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -10640,12 +11227,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>запас после поступления 73.311 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-10 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 73.311 т превышает ёмкость хранилища Base storage 70.0 т в 2039-10 (поставка одной партией в начале месяца; запас на начало 45.925 т, нетто-поступление 27.386 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -10682,12 +11269,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>запас после поступления 74.030 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-11 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 74.030 т превышает ёмкость хранилища Base storage 70.0 т в 2039-11 (поставка одной партией в начале месяца; запас на начало 46.644 т, нетто-поступление 27.386 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -10724,12 +11311,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>запас после поступления 74.749 т превышает ёмкость хранилища Base storage 70.0 т внутри 2039-12 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 74.749 т превышает ёмкость хранилища Base storage 70.0 т в 2039-12 (поставка одной партией в начале месяца; запас на начало 47.363 т, нетто-поступление 27.386 т, выдача 26.667 т)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -10766,12 +11353,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-01 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-01 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -10781,13 +11368,13 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>80.58261141666667</v>
+        <v>80.58261141666668</v>
       </c>
       <c r="J9" t="n">
         <v>70</v>
       </c>
       <c r="K9" t="n">
-        <v>10.58261141666667</v>
+        <v>10.58261141666668</v>
       </c>
     </row>
     <row r="10">
@@ -10808,12 +11395,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-02 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-02 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -10823,13 +11410,13 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>80.58261433333332</v>
+        <v>80.58261433333334</v>
       </c>
       <c r="J10" t="n">
         <v>70</v>
       </c>
       <c r="K10" t="n">
-        <v>10.58261433333332</v>
+        <v>10.58261433333334</v>
       </c>
     </row>
     <row r="11">
@@ -10850,12 +11437,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-03 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-03 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -10865,13 +11452,13 @@
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>80.58261724999998</v>
+        <v>80.58261725</v>
       </c>
       <c r="J11" t="n">
         <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>10.58261724999998</v>
+        <v>10.58261725</v>
       </c>
     </row>
     <row r="12">
@@ -10892,12 +11479,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-04 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-04 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -10907,13 +11494,13 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>80.58262016666664</v>
+        <v>80.58262016666666</v>
       </c>
       <c r="J12" t="n">
         <v>70</v>
       </c>
       <c r="K12" t="n">
-        <v>10.58262016666664</v>
+        <v>10.58262016666666</v>
       </c>
     </row>
     <row r="13">
@@ -10934,12 +11521,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-05 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-05 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -10949,13 +11536,13 @@
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>80.5826230833333</v>
+        <v>80.58262308333332</v>
       </c>
       <c r="J13" t="n">
         <v>70</v>
       </c>
       <c r="K13" t="n">
-        <v>10.5826230833333</v>
+        <v>10.58262308333332</v>
       </c>
     </row>
     <row r="14">
@@ -10976,12 +11563,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-06 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-06 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -10991,13 +11578,13 @@
         <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>80.58262599999996</v>
+        <v>80.58262599999998</v>
       </c>
       <c r="J14" t="n">
         <v>70</v>
       </c>
       <c r="K14" t="n">
-        <v>10.58262599999996</v>
+        <v>10.58262599999998</v>
       </c>
     </row>
     <row r="15">
@@ -11018,12 +11605,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-07 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-07 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -11033,13 +11620,13 @@
         <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>80.58262891666662</v>
+        <v>80.58262891666664</v>
       </c>
       <c r="J15" t="n">
         <v>70</v>
       </c>
       <c r="K15" t="n">
-        <v>10.58262891666662</v>
+        <v>10.58262891666664</v>
       </c>
     </row>
     <row r="16">
@@ -11060,12 +11647,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-08 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-08 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -11075,13 +11662,13 @@
         <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>80.58263183333328</v>
+        <v>80.58263183333329</v>
       </c>
       <c r="J16" t="n">
         <v>70</v>
       </c>
       <c r="K16" t="n">
-        <v>10.58263183333328</v>
+        <v>10.58263183333329</v>
       </c>
     </row>
     <row r="17">
@@ -11102,12 +11689,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-09 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-09 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -11117,13 +11704,13 @@
         <v>9</v>
       </c>
       <c r="I17" t="n">
-        <v>80.58263474999994</v>
+        <v>80.58263474999995</v>
       </c>
       <c r="J17" t="n">
         <v>70</v>
       </c>
       <c r="K17" t="n">
-        <v>10.58263474999994</v>
+        <v>10.58263474999995</v>
       </c>
     </row>
     <row r="18">
@@ -11144,12 +11731,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-10 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-10 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -11159,13 +11746,13 @@
         <v>10</v>
       </c>
       <c r="I18" t="n">
-        <v>80.5826376666666</v>
+        <v>80.58263766666661</v>
       </c>
       <c r="J18" t="n">
         <v>70</v>
       </c>
       <c r="K18" t="n">
-        <v>10.5826376666666</v>
+        <v>10.58263766666661</v>
       </c>
     </row>
     <row r="19">
@@ -11186,12 +11773,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-11 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-11 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -11201,13 +11788,13 @@
         <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>80.58264058333326</v>
+        <v>80.58264058333327</v>
       </c>
       <c r="J19" t="n">
         <v>70</v>
       </c>
       <c r="K19" t="n">
-        <v>10.58264058333326</v>
+        <v>10.58264058333327</v>
       </c>
     </row>
     <row r="20">
@@ -11228,12 +11815,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>warning</t>
+          <t>hard</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>запас после поступления 80.583 т превышает ёмкость хранилища Base storage 70.0 т внутри 2040-12 (до выдачи потребителям)</t>
+          <t>пик запаса внутри месяца 80.583 т превышает ёмкость хранилища Base storage 70.0 т в 2040-12 (поставка одной партией в начале месяца; запас на начало 48.083 т, нетто-поступление 32.500 т, выдача 32.500 т)</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -11243,13 +11830,13 @@
         <v>12</v>
       </c>
       <c r="I20" t="n">
-        <v>80.58264349999992</v>
+        <v>80.58264349999993</v>
       </c>
       <c r="J20" t="n">
         <v>70</v>
       </c>
       <c r="K20" t="n">
-        <v>10.58264349999992</v>
+        <v>10.58264349999993</v>
       </c>
     </row>
   </sheetData>
@@ -11263,7 +11850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12954,7 +13541,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -12962,14 +13549,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -12986,7 +13573,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13590,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -13011,14 +13598,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>109.876</v>
       </c>
       <c r="G37" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -13052,7 +13639,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -13060,18 +13647,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -13081,7 +13669,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -13096,7 +13688,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -13104,7 +13696,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -13140,27 +13732,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -13170,11 +13761,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -13189,7 +13776,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -13197,14 +13784,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -13221,7 +13808,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13825,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -13246,14 +13833,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G42" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -13270,7 +13857,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13287,7 +13874,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -13295,170 +13882,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G44" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>30.82226200000003</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>190</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13473,7 +14060,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -13481,14 +14068,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>30.82226200000003</v>
       </c>
       <c r="G47" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -13505,7 +14092,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13522,7 +14109,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -13530,14 +14117,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>16.699</v>
+        <v>46.65559533333337</v>
       </c>
       <c r="G48" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -13554,7 +14141,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2037-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13571,7 +14158,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -13579,14 +14166,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>16.6988</v>
+        <v>190</v>
       </c>
       <c r="G49" t="n">
-        <v>16.699</v>
+        <v>190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -13603,7 +14190,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13620,7 +14207,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -13628,219 +14215,219 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>190</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>16.699</v>
+      </c>
+      <c r="G51" t="n">
+        <v>130</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>16.6988</v>
+      </c>
+      <c r="G52" t="n">
+        <v>16.699</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <f>=</f>
         <v/>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D54" t="n">
         <v>2037</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54">
         <f>=</f>
         <v/>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>39.45240150000002</v>
-      </c>
-      <c r="G52" t="n">
-        <v>70</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>190</v>
-      </c>
-      <c r="G53" t="n">
-        <v>190</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>190</v>
-      </c>
-      <c r="G54" t="n">
-        <v>190</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13855,7 +14442,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -13863,14 +14450,14 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>80.81699999999999</v>
+        <v>39.45240150000002</v>
       </c>
       <c r="G55" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -13887,7 +14474,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13904,7 +14491,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -13912,14 +14499,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>80.8169</v>
+        <v>60.28573483333336</v>
       </c>
       <c r="G56" t="n">
-        <v>80.81699999999999</v>
+        <v>70</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -13936,7 +14523,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2038-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13953,7 +14540,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -13961,268 +14548,268 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>190</v>
+      </c>
+      <c r="G57" t="n">
+        <v>190</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>190</v>
+      </c>
+      <c r="G58" t="n">
+        <v>190</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>80.81699999999999</v>
+      </c>
+      <c r="G59" t="n">
+        <v>130</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>80.8169</v>
+      </c>
+      <c r="G60" t="n">
+        <v>80.81699999999999</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57">
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61">
         <f>=</f>
         <v/>
       </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D62" t="n">
         <v>2038</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62">
         <f>=</f>
         <v/>
       </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>48.08260850000001</v>
-      </c>
-      <c r="G59" t="n">
-        <v>70</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>190</v>
-      </c>
-      <c r="G60" t="n">
-        <v>190</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>190</v>
-      </c>
-      <c r="G61" t="n">
-        <v>190</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>24.116</v>
-      </c>
-      <c r="G62" t="n">
-        <v>110</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -14237,7 +14824,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -14245,14 +14832,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>24.1154</v>
+        <v>48.08260850000001</v>
       </c>
       <c r="G63" t="n">
-        <v>24.116</v>
+        <v>70</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -14269,7 +14856,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14873,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -14294,14 +14881,14 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>130</v>
+        <v>74.74927516666668</v>
       </c>
       <c r="G64" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -14309,7 +14896,7 @@
         </is>
       </c>
       <c r="I64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -14318,7 +14905,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2039-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14922,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -14343,14 +14930,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="G65" t="n">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -14367,7 +14954,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14971,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -14392,317 +14979,317 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>190</v>
+      </c>
+      <c r="G66" t="n">
+        <v>190</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>24.116</v>
+      </c>
+      <c r="G67" t="n">
+        <v>110</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>24.1154</v>
+      </c>
+      <c r="G68" t="n">
+        <v>24.116</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>130</v>
+      </c>
+      <c r="G69" t="n">
+        <v>130</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>130</v>
+      </c>
+      <c r="G70" t="n">
+        <v>130</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66">
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71">
         <f>=</f>
         <v/>
       </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D72" t="n">
         <v>2039</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67">
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72">
         <f>=</f>
         <v/>
       </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>48.08264349999992</v>
-      </c>
-      <c r="G68" t="n">
-        <v>70</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2040-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>190</v>
-      </c>
-      <c r="G69" t="n">
-        <v>190</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>190</v>
-      </c>
-      <c r="G70" t="n">
-        <v>190</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>88.377</v>
-      </c>
-      <c r="G71" t="n">
-        <v>110</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>88.377</v>
-      </c>
-      <c r="G72" t="n">
-        <v>88.377</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -14717,7 +15304,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -14725,14 +15312,14 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>130</v>
+        <v>48.08264349999992</v>
       </c>
       <c r="G73" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -14749,7 +15336,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14766,7 +15353,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -14774,14 +15361,14 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>130</v>
+        <v>80.58264349999993</v>
       </c>
       <c r="G74" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -14789,7 +15376,7 @@
         </is>
       </c>
       <c r="I74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -14798,7 +15385,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2040-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14815,7 +15402,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -14823,72 +15410,366 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>190</v>
+      </c>
+      <c r="G75" t="n">
+        <v>190</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>190</v>
+      </c>
+      <c r="G76" t="n">
+        <v>190</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>88.377</v>
+      </c>
+      <c r="G77" t="n">
+        <v>110</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>88.377</v>
+      </c>
+      <c r="G78" t="n">
+        <v>88.377</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>130</v>
+      </c>
+      <c r="G79" t="n">
+        <v>130</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>130</v>
+      </c>
+      <c r="G80" t="n">
+        <v>130</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75">
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81">
         <f>=</f>
         <v/>
       </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>P2_earth_new</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D82" t="n">
         <v>2040</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76">
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82">
         <f>=</f>
         <v/>
       </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23627,7 +24508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23669,7 +24550,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11079.23505658</v>
+        <v>11079.60492235</v>
       </c>
     </row>
     <row r="3">
@@ -23689,7 +24570,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8779.821578741019</v>
+        <v>8780.19144451102</v>
       </c>
     </row>
     <row r="4">
@@ -23829,7 +24710,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.97067270257554</v>
+        <v>7.970938793057555</v>
       </c>
     </row>
     <row r="11">
@@ -23849,7 +24730,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.316418401971956</v>
+        <v>6.316684492453971</v>
       </c>
     </row>
     <row r="12">
@@ -24009,7 +24890,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>136.2588265800001</v>
+        <v>136.6286923500001</v>
       </c>
     </row>
     <row r="20">
@@ -24125,11 +25006,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -24145,11 +25026,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -24165,7 +25046,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -24185,11 +25066,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -24205,11 +25086,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -24225,11 +25106,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P2_earth_new</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>75</v>
+      <c r="D32" t="n">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
